--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H706"/>
+  <dimension ref="A1:H710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21620,6 +21620,126 @@
       <c r="H706" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="C707" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="D707" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="E707" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="F707" t="n">
+        <v>361.27</v>
+      </c>
+      <c r="G707" t="n">
+        <v>358.11</v>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:43+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="C708" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="D708" t="n">
+        <v>363.94</v>
+      </c>
+      <c r="E708" t="n">
+        <v>356.88</v>
+      </c>
+      <c r="F708" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="G708" t="n">
+        <v>357.18</v>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>372.02</v>
+      </c>
+      <c r="C709" t="n">
+        <v>356.56</v>
+      </c>
+      <c r="D709" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="E709" t="n">
+        <v>356.63</v>
+      </c>
+      <c r="F709" t="n">
+        <v>360.16</v>
+      </c>
+      <c r="G709" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="C710" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="D710" t="n">
+        <v>363.11</v>
+      </c>
+      <c r="E710" t="n">
+        <v>356.01</v>
+      </c>
+      <c r="F710" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="G710" t="n">
+        <v>356.64</v>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29027,6 +29147,46 @@
       </c>
       <c r="B739" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -29195,28 +29355,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07510796332082577</v>
+        <v>-0.07547762510805499</v>
       </c>
       <c r="J2" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K2" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04568373183066399</v>
+        <v>0.04664659745345123</v>
       </c>
       <c r="M2" t="n">
-        <v>2.017175167638159</v>
+        <v>2.007689003186445</v>
       </c>
       <c r="N2" t="n">
-        <v>6.685097221015173</v>
+        <v>6.648616081379094</v>
       </c>
       <c r="O2" t="n">
-        <v>2.585555495636319</v>
+        <v>2.578491047372299</v>
       </c>
       <c r="P2" t="n">
-        <v>374.1291410174591</v>
+        <v>374.1331035403934</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29273,28 +29433,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09733046156343179</v>
+        <v>0.09641686402618296</v>
       </c>
       <c r="J3" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K3" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09921899478357099</v>
+        <v>0.09855293180993618</v>
       </c>
       <c r="M3" t="n">
-        <v>1.754816652512725</v>
+        <v>1.749506233536309</v>
       </c>
       <c r="N3" t="n">
-        <v>4.878956718125734</v>
+        <v>4.855540017510088</v>
       </c>
       <c r="O3" t="n">
-        <v>2.20883605505835</v>
+        <v>2.203528991756198</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7885597931395</v>
+        <v>354.7983496276003</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29351,28 +29511,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04826588209237682</v>
+        <v>0.0483777711546591</v>
       </c>
       <c r="J4" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K4" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02044874656864004</v>
+        <v>0.02078704116843177</v>
       </c>
       <c r="M4" t="n">
-        <v>1.95911955103993</v>
+        <v>1.949912695636254</v>
       </c>
       <c r="N4" t="n">
-        <v>6.330615987042981</v>
+        <v>6.295598736926727</v>
       </c>
       <c r="O4" t="n">
-        <v>2.516071538538398</v>
+        <v>2.509103173830587</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2585451987602</v>
+        <v>362.257348709287</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29429,28 +29589,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05541480047336277</v>
+        <v>-0.05517685533392625</v>
       </c>
       <c r="J5" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K5" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01869153870290663</v>
+        <v>0.01875544573101762</v>
       </c>
       <c r="M5" t="n">
-        <v>2.485361618332426</v>
+        <v>2.473764489172231</v>
       </c>
       <c r="N5" t="n">
-        <v>9.145701858826429</v>
+        <v>9.095458826315973</v>
       </c>
       <c r="O5" t="n">
-        <v>3.02418614817713</v>
+        <v>3.015867839663398</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9577022391805</v>
+        <v>357.9551562310931</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29507,28 +29667,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03165879555137384</v>
+        <v>-0.03297981597274149</v>
       </c>
       <c r="J6" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K6" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005160606207674778</v>
+        <v>0.005661056028485767</v>
       </c>
       <c r="M6" t="n">
-        <v>2.670846645291238</v>
+        <v>2.663089422783837</v>
       </c>
       <c r="N6" t="n">
-        <v>10.96089539250486</v>
+        <v>10.90923516591645</v>
       </c>
       <c r="O6" t="n">
-        <v>3.310724300286096</v>
+        <v>3.302913133268336</v>
       </c>
       <c r="P6" t="n">
-        <v>362.3734916159955</v>
+        <v>362.3876500016123</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29585,28 +29745,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1086074697120435</v>
+        <v>-0.1105574651955075</v>
       </c>
       <c r="J7" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="K7" t="n">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04388577954926509</v>
+        <v>0.04587887332288798</v>
       </c>
       <c r="M7" t="n">
-        <v>3.118578744004892</v>
+        <v>3.111002930184695</v>
       </c>
       <c r="N7" t="n">
-        <v>14.57841653616122</v>
+        <v>14.51535847753678</v>
       </c>
       <c r="O7" t="n">
-        <v>3.818169264996147</v>
+        <v>3.809902686098003</v>
       </c>
       <c r="P7" t="n">
-        <v>361.9921988841717</v>
+        <v>362.0130955455486</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29644,7 +29804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H706"/>
+  <dimension ref="A1:H710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59299,6 +59459,174 @@
         </is>
       </c>
     </row>
+    <row r="707">
+      <c r="A707" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>-41.069731069496484,174.85343896483434</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>-41.06904017627976,174.85339104033272</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>-41.06842807884717,174.8530644240773</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>-41.06783159480177,174.85267576575504</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>-41.06729068476998,174.8521465056612</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>-41.06674004129382,174.85162939758368</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:06:43+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>-41.069731069496484,174.85343896483434</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>-41.06904017627976,174.85339104033272</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>-41.06842807884717,174.8530644240773</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>-41.06782997134722,174.85267905474</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>-41.06728519369091,174.85215638325613</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>-41.06673482880803,174.85163805905103</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:44+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>-41.069731304728656,174.85343781620796</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>-41.06903969919836,174.85339321153106</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>-41.0684270251796,174.85306745100877</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-41.067828741457355,174.8526815463952</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>-41.06728476719928,174.8521571504479</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>-41.06673494090451,174.8516378727829</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-41.06972937582439,174.85344723494416</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-41.069038920802306,174.85339675401246</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-41.068424955475216,174.8530733967667</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-41.06782569133026,174.8526877256996</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-41.06728167513495,174.85216271258795</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-41.0667318022031,174.85164308828948</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H710"/>
+  <dimension ref="A1:H714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21738,6 +21738,126 @@
         <v>356.64</v>
       </c>
       <c r="H710" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="C711" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="D711" t="n">
+        <v>363.08</v>
+      </c>
+      <c r="E711" t="n">
+        <v>355.95</v>
+      </c>
+      <c r="F711" t="n">
+        <v>359.86</v>
+      </c>
+      <c r="G711" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>371.75</v>
+      </c>
+      <c r="C712" t="n">
+        <v>355.92</v>
+      </c>
+      <c r="D712" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="E712" t="n">
+        <v>355</v>
+      </c>
+      <c r="F712" t="n">
+        <v>359.13</v>
+      </c>
+      <c r="G712" t="n">
+        <v>356.45</v>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="C713" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="D713" t="n">
+        <v>361.94</v>
+      </c>
+      <c r="E713" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="F713" t="n">
+        <v>358.55</v>
+      </c>
+      <c r="G713" t="n">
+        <v>355.99</v>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>370.67</v>
+      </c>
+      <c r="C714" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="D714" t="n">
+        <v>361.4</v>
+      </c>
+      <c r="E714" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="F714" t="n">
+        <v>357.84</v>
+      </c>
+      <c r="G714" t="n">
+        <v>355.18</v>
+      </c>
+      <c r="H714" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21754,7 +21874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29187,6 +29307,46 @@
       </c>
       <c r="B743" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -29355,28 +29515,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07547762510805499</v>
+        <v>-0.07636154531751499</v>
       </c>
       <c r="J2" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="K2" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04664659745345123</v>
+        <v>0.04821143013688911</v>
       </c>
       <c r="M2" t="n">
-        <v>2.007689003186445</v>
+        <v>2.000895508607281</v>
       </c>
       <c r="N2" t="n">
-        <v>6.648616081379094</v>
+        <v>6.616364505197373</v>
       </c>
       <c r="O2" t="n">
-        <v>2.578491047372299</v>
+        <v>2.57222948144161</v>
       </c>
       <c r="P2" t="n">
-        <v>374.1331035403934</v>
+        <v>374.1426113012233</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29433,28 +29593,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09641686402618296</v>
+        <v>0.09461330787206855</v>
       </c>
       <c r="J3" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="K3" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09855293180993618</v>
+        <v>0.09600901222896063</v>
       </c>
       <c r="M3" t="n">
-        <v>1.749506233536309</v>
+        <v>1.748691992012015</v>
       </c>
       <c r="N3" t="n">
-        <v>4.855540017510088</v>
+        <v>4.844356413067045</v>
       </c>
       <c r="O3" t="n">
-        <v>2.203528991756198</v>
+        <v>2.200989871186836</v>
       </c>
       <c r="P3" t="n">
-        <v>354.7983496276003</v>
+        <v>354.8177418070936</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29511,28 +29671,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0483777711546591</v>
+        <v>0.04694006050574685</v>
       </c>
       <c r="J4" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="K4" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02078704116843177</v>
+        <v>0.0197908730678592</v>
       </c>
       <c r="M4" t="n">
-        <v>1.949912695636254</v>
+        <v>1.946218176078301</v>
       </c>
       <c r="N4" t="n">
-        <v>6.295598736926727</v>
+        <v>6.27221034259201</v>
       </c>
       <c r="O4" t="n">
-        <v>2.509103173830587</v>
+        <v>2.504438129120384</v>
       </c>
       <c r="P4" t="n">
-        <v>362.257348709287</v>
+        <v>362.2728115051615</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29589,28 +29749,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05517685533392625</v>
+        <v>-0.05697187411684745</v>
       </c>
       <c r="J5" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="K5" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01875544573101762</v>
+        <v>0.02016895987325318</v>
       </c>
       <c r="M5" t="n">
-        <v>2.473764489172231</v>
+        <v>2.469710853528821</v>
       </c>
       <c r="N5" t="n">
-        <v>9.095458826315973</v>
+        <v>9.062921931811443</v>
       </c>
       <c r="O5" t="n">
-        <v>3.015867839663398</v>
+        <v>3.010468722941901</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9551562310931</v>
+        <v>357.9744616954748</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29667,28 +29827,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03297981597274149</v>
+        <v>-0.03584667591229872</v>
       </c>
       <c r="J6" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="K6" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005661056028485767</v>
+        <v>0.006736304470448373</v>
       </c>
       <c r="M6" t="n">
-        <v>2.663089422783837</v>
+        <v>2.66397319669425</v>
       </c>
       <c r="N6" t="n">
-        <v>10.90923516591645</v>
+        <v>10.88980662865034</v>
       </c>
       <c r="O6" t="n">
-        <v>3.302913133268336</v>
+        <v>3.299970701180593</v>
       </c>
       <c r="P6" t="n">
-        <v>362.3876500016123</v>
+        <v>362.4184770759229</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29745,28 +29905,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1105574651955075</v>
+        <v>-0.1136761212224798</v>
       </c>
       <c r="J7" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="K7" t="n">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04587887332288798</v>
+        <v>0.04878264805405474</v>
       </c>
       <c r="M7" t="n">
-        <v>3.111002930184695</v>
+        <v>3.109661643077238</v>
       </c>
       <c r="N7" t="n">
-        <v>14.51535847753678</v>
+        <v>14.48212931773123</v>
       </c>
       <c r="O7" t="n">
-        <v>3.809902686098003</v>
+        <v>3.805539293941298</v>
       </c>
       <c r="P7" t="n">
-        <v>362.0130955455486</v>
+        <v>362.046628154316</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29804,7 +29964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H710"/>
+  <dimension ref="A1:H714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59627,6 +59787,174 @@
         </is>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-41.0697307636946,174.85344045804865</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-41.06903884547366,174.85339709683328</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-41.068424842582225,174.85307372108073</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-41.067825396156664,174.85268832369675</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-41.0672831678557,174.85216002741697</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-41.0667335957468,174.85164010800008</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:06:38+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-41.06973066960173,174.8534409174992</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-41.069038092187036,174.853400525041</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-41.068422735246536,174.85307977494293</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-41.067820722574155,174.85269779198458</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-41.06727927611932,174.85216702804107</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-41.066730737286505,174.85164485783622</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-41.0697286701275,174.8534506808231</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-41.06903706269516,174.8534052102581</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-41.06842055264851,174.85308604501407</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-41.06781777083745,174.85270377195513</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-41.06727618405452,174.85217259018017</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-41.066728159067246,174.8516491420018</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-41.069728129093164,174.8534533226636</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-41.06903651028481,174.853407724277</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>-41.0684185205742,174.85309188266612</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>-41.06781516346977,174.85270905426202</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>-41.067272398940354,174.8521793990049</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>-41.06672361915908,174.85165668585782</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0338/nzd0338.xlsx
+++ b/data/nzd0338/nzd0338.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H714"/>
+  <dimension ref="A1:H717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21858,6 +21858,96 @@
         <v>355.18</v>
       </c>
       <c r="H714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>370.33</v>
+      </c>
+      <c r="C715" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="D715" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="E715" t="n">
+        <v>353.51</v>
+      </c>
+      <c r="F715" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="G715" t="n">
+        <v>354.9</v>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>369.94</v>
+      </c>
+      <c r="C716" t="n">
+        <v>355.08</v>
+      </c>
+      <c r="D716" t="n">
+        <v>360.39</v>
+      </c>
+      <c r="E716" t="n">
+        <v>352.49</v>
+      </c>
+      <c r="F716" t="n">
+        <v>356.69</v>
+      </c>
+      <c r="G716" t="n">
+        <v>354.35</v>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>370.88</v>
+      </c>
+      <c r="C717" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="D717" t="n">
+        <v>360.04</v>
+      </c>
+      <c r="E717" t="n">
+        <v>352.29</v>
+      </c>
+      <c r="F717" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="G717" t="n">
+        <v>353.95</v>
+      </c>
+      <c r="H717" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21874,7 +21964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B747"/>
+  <dimension ref="A1:B750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29347,6 +29437,36 @@
       </c>
       <c r="B747" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.29</v>
       </c>
     </row>
   </sheetData>
@@ -29515,28 +29635,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07636154531751499</v>
+        <v>-0.0777221324286571</v>
       </c>
       <c r="J2" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K2" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04821143013688911</v>
+        <v>0.0501973205382833</v>
       </c>
       <c r="M2" t="n">
-        <v>2.000895508607281</v>
+        <v>1.999332136442619</v>
       </c>
       <c r="N2" t="n">
-        <v>6.616364505197373</v>
+        <v>6.601072940927413</v>
       </c>
       <c r="O2" t="n">
-        <v>2.57222948144161</v>
+        <v>2.569255328091666</v>
       </c>
       <c r="P2" t="n">
-        <v>374.1426113012233</v>
+        <v>374.1572799919736</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29593,28 +29713,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09461330787206855</v>
+        <v>0.09294679732021488</v>
       </c>
       <c r="J3" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K3" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09600901222896063</v>
+        <v>0.09341597530498458</v>
       </c>
       <c r="M3" t="n">
-        <v>1.748691992012015</v>
+        <v>1.749783273617593</v>
       </c>
       <c r="N3" t="n">
-        <v>4.844356413067045</v>
+        <v>4.842036187464753</v>
       </c>
       <c r="O3" t="n">
-        <v>2.200989871186836</v>
+        <v>2.200462721216779</v>
       </c>
       <c r="P3" t="n">
-        <v>354.8177418070936</v>
+        <v>354.8357092810451</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29671,28 +29791,28 @@
         <v>0.1762</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04694006050574685</v>
+        <v>0.04450709644695099</v>
       </c>
       <c r="J4" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K4" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0197908730678592</v>
+        <v>0.01787817877492315</v>
       </c>
       <c r="M4" t="n">
-        <v>1.946218176078301</v>
+        <v>1.95040509788977</v>
       </c>
       <c r="N4" t="n">
-        <v>6.27221034259201</v>
+        <v>6.284530986225608</v>
       </c>
       <c r="O4" t="n">
-        <v>2.504438129120384</v>
+        <v>2.506896684393995</v>
       </c>
       <c r="P4" t="n">
-        <v>362.2728115051615</v>
+        <v>362.2990496205965</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29749,28 +29869,28 @@
         <v>0.1963</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05697187411684745</v>
+        <v>-0.05992496695570937</v>
       </c>
       <c r="J5" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K5" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02016895987325318</v>
+        <v>0.02232620051935674</v>
       </c>
       <c r="M5" t="n">
-        <v>2.469710853528821</v>
+        <v>2.475490346131112</v>
       </c>
       <c r="N5" t="n">
-        <v>9.062921931811443</v>
+        <v>9.081697331349153</v>
       </c>
       <c r="O5" t="n">
-        <v>3.010468722941901</v>
+        <v>3.013585461099312</v>
       </c>
       <c r="P5" t="n">
-        <v>357.9744616954748</v>
+        <v>358.0063086953805</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29827,28 +29947,28 @@
         <v>0.1494</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.03584667591229872</v>
+        <v>-0.03961007913363233</v>
       </c>
       <c r="J6" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K6" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006736304470448373</v>
+        <v>0.008217795566316966</v>
       </c>
       <c r="M6" t="n">
-        <v>2.66397319669425</v>
+        <v>2.673779541980556</v>
       </c>
       <c r="N6" t="n">
-        <v>10.88980662865034</v>
+        <v>10.93565146348534</v>
       </c>
       <c r="O6" t="n">
-        <v>3.299970701180593</v>
+        <v>3.306909654569556</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4184770759229</v>
+        <v>362.4590614586041</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29905,28 +30025,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1136761212224798</v>
+        <v>-0.1173533712418842</v>
       </c>
       <c r="J7" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K7" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04878264805405474</v>
+        <v>0.05197200583516126</v>
       </c>
       <c r="M7" t="n">
-        <v>3.109661643077238</v>
+        <v>3.115717571454794</v>
       </c>
       <c r="N7" t="n">
-        <v>14.48212931773123</v>
+        <v>14.50825182970688</v>
       </c>
       <c r="O7" t="n">
-        <v>3.805539293941298</v>
+        <v>3.808969917143857</v>
       </c>
       <c r="P7" t="n">
-        <v>362.046628154316</v>
+        <v>362.0862820081924</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29964,7 +30084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H714"/>
+  <dimension ref="A1:H717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59955,6 +60075,132 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:52+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-41.069727329303156,174.85345722799292</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-41.06903625918918,174.8534088670128</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>-41.06841754216794,174.85309469338733</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>-41.06781339242744,174.8527126422438</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>-41.06727047972739,174.85218285136645</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-41.06672204980799,174.85165929361025</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:06:48+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-41.06972641189681,174.85346170763523</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-41.069035982983976,174.85341012402222</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-41.06841471984182,174.85310280123656</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-41.0678083744736,174.85272280819115</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>-41.06726626812083,174.85219042738134</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>-41.06671896715391,174.85166441598076</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:01:05+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>-41.06972862308104,174.85345091054836</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>-41.069037439338544,174.8534034961543</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>-41.06841340275612,174.85310658489928</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>-41.067807390560965,174.85272480151397</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>-41.06726344261235,174.85219551002368</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>-41.066716725223536,174.8516681413408</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
